--- a/Result/profitability/1229.xlsx
+++ b/Result/profitability/1229.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.54625</v>
+        <v>0.5725</v>
       </c>
       <c r="N2" t="n">
-        <v>19.82375</v>
+        <v>20.3125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5525</v>
+        <v>0.56125</v>
       </c>
       <c r="N3" t="n">
-        <v>18.675</v>
+        <v>18.99125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0.50625</v>
+        <v>0.51875</v>
       </c>
       <c r="N4" t="n">
-        <v>16.65875</v>
+        <v>17.13875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0.36</v>
+        <v>0.345</v>
       </c>
       <c r="N5" t="n">
-        <v>14.00125</v>
+        <v>11.7425</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.26875</v>
+        <v>0.26125</v>
       </c>
       <c r="N6" t="n">
-        <v>9.772499999999999</v>
+        <v>9.516250000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.24375</v>
+        <v>0.25375</v>
       </c>
       <c r="N7" t="n">
-        <v>8.40625</v>
+        <v>8.18</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0.20875</v>
+        <v>0.22125</v>
       </c>
       <c r="N8" t="n">
-        <v>7.22</v>
+        <v>6.718749999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.2375</v>
       </c>
       <c r="N9" t="n">
-        <v>5.806249999999999</v>
+        <v>5.80625</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.24375</v>
       </c>
       <c r="N10" t="n">
-        <v>6.149999999999999</v>
+        <v>6.15</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.26875</v>
       </c>
       <c r="N11" t="n">
-        <v>5.793749999999999</v>
+        <v>5.79375</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2511</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E75" t="n">
+        <v>485</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>147</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.87%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1238</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1386</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1186</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6025</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.2675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1818181818181817</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.010000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1719554030874786</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1558441558441558</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-18.07</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4834135901551633</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
